--- a/artifacts/enterprise_review.xlsx
+++ b/artifacts/enterprise_review.xlsx
@@ -457,8 +457,9 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Хорошо, мне нужно выделить ключевые требования безопасности из предоставленных документов и дать краткое резюме. Начну с первого документа, doc-safety-01. Там говорится, что все электрическое оборудование должно включать заземление и устройства экстренной остановки. Также указано, что периодическая инспекция проводится каждые 6 месяцев. Это важные пункты, которые нужно отметить.
-Теперь второй документ, doc-safety-02. Там обязательное обучение операторов перед вводом в эксплуатацию и нео</t>
+Хорошо, мне нужно обработать запрос пользователя, который просит выделить ключевые требования безопасности и дать краткое резюме. Давайте посмотрим на предоставленные документы.
+Первый документ (doc-safety-01) говорит, что все электрическое оборудование должно иметь заземление и устройства экстренной остановки. Периодическая инспекция каждые 6 месяцев. Это важные технические требования, которые касаются безопасности оборудования и регулярного обслуживания.
+Второй документ (doc-safety-0</t>
         </is>
       </c>
     </row>
@@ -481,8 +482,8 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Хорошо, мне нужно найти потенциальные риски несоответствия на основе предоставленных документов и предложить приоритетные действия. Начну с анализа каждого из документов.
-Первый документ (doc-safety-01) гласит, что все электрическое оборудование должно включать заземление и устройства экстренной остановки, а также требует периодической инспекции каждые 6 месяцев. Если эти требования не соблюдаются, это может привести к рискам безопасности, например, поражению электрическим током или нев</t>
+Хорошо, мне нужно найти потенциальные риски несоответствия и предложить приоритетные действия на основе предоставленных документов. Давайте посмотрим на нормативные документы.
+Первый документ (doc-safety-01) требует, чтобы все электрическое оборудование имело заземление и устройства экстренной остановки, а также периодическую инспекцию каждые 6 месяцев. Если это не соблюдается, возможны риски безопасности, например, поражение электрическим током или несчастные случаи из-за отказа оборуд</t>
         </is>
       </c>
     </row>
